--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,19 +453,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4841603241809979</v>
+        <v>1.391031980694962</v>
       </c>
       <c r="C2" t="n">
+        <v>0.1357915304721569</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.003642472676483447</v>
-      </c>
       <c r="E2" t="n">
-        <v>1.317547585021377e-06</v>
+        <v>0.07461260996186911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04825809057082037</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,16 +453,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.391031980694962</v>
+        <v>1.406382439326014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1357915304721569</v>
+        <v>0.5296187857592148</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07461260996186911</v>
+        <v>0.07461260976955639</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,19 +453,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.406382439326014</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5296187857592148</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07461260976955639</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.4878048780487805</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.407526839642322</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -465,7 +465,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4878048780487805</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,16 +453,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.407526839642322</v>
+        <v>2.471503203273254</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1852550364996299</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.11038009145463</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.471503203273254</v>
+        <v>2.471503174528505</v>
       </c>
       <c r="C2" t="n">
         <v>0.1852550364996299</v>
@@ -462,7 +462,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11038009145463</v>
+        <v>0.1103801201993786</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -450,22 +450,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>0.0001412526301437265</v>
       </c>
       <c r="B2" t="n">
-        <v>2.471503174528505</v>
+        <v>0.9329649128919539</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1852550364996299</v>
+        <v>0.1378556983081443</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.050100798331301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1103801201993786</v>
+        <v>0.07434178915609041</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.8459403920442028</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -450,22 +450,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0001412526301437265</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9329649128919539</v>
+        <v>0.5926757300551306</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1378556983081443</v>
+        <v>0.1359293671302275</v>
       </c>
       <c r="D2" t="n">
-        <v>1.050100798331301</v>
+        <v>0.2283419049843569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07434178915609041</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8459403920442028</v>
+        <v>0.09842726450032753</v>
       </c>
     </row>
   </sheetData>

--- a/6node_spain/output_s.xlsx
+++ b/6node_spain/output_s.xlsx
@@ -453,19 +453,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5926757300551306</v>
+        <v>0.5227848035737043</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1359293671302275</v>
+        <v>0.1360196946354306</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2283419049843569</v>
+        <v>0.2282864457862377</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09842726450032753</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
